--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130148186</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130148294</v>
       </c>
       <c r="B2" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130148186</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>130150005</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,2207 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130297821</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>490358</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6688096</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ganska färska hackspår.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130298224</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>490361</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6688015</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130297899</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>490357</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6688094</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130297823</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490352</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6688068</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130297886</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490364</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6688081</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130297967</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490493</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6687991</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bladrosetter över ca 5 kvdm.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130298148</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490478</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6687986</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Barkfläk gran, hagelsalva.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130297824</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57667</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490349</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6688055</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130297865</v>
+      </c>
+      <c r="B13" t="n">
+        <v>81165</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490429</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6687934</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130297822</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490363</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6688092</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130297999</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>490490</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6687978</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Riktigt över större yta.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130298189</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490428</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6687892</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130298036</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>490489</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6687960</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130298072</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490442</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6687947</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130298026</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490503</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6687970</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130297996</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>490492</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6687981</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spridda över ca 1 kvm.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130298069</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>490458</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6687937</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130297829</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490409</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6687932</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130297890</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490365</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6688077</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297899</v>
+        <v>130297823</v>
       </c>
       <c r="B7" t="n">
         <v>57823</v>
@@ -1290,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490357</v>
+        <v>490352</v>
       </c>
       <c r="R7" t="n">
-        <v>6688094</v>
+        <v>6688068</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130297823</v>
+        <v>130297899</v>
       </c>
       <c r="B8" t="n">
         <v>57823</v>
@@ -1402,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490352</v>
+        <v>490357</v>
       </c>
       <c r="R8" t="n">
-        <v>6688068</v>
+        <v>6688094</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1843,50 +1843,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B12" t="n">
-        <v>57667</v>
+        <v>81165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R12" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,45 +1950,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B13" t="n">
-        <v>81165</v>
+        <v>57667</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R13" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2035,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2525,7 +2525,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298072</v>
+        <v>130298069</v>
       </c>
       <c r="B18" t="n">
         <v>57826</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490442</v>
+        <v>490458</v>
       </c>
       <c r="R18" t="n">
-        <v>6687947</v>
+        <v>6687937</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298026</v>
+        <v>130298072</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,16 +2653,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2673,7 +2673,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490503</v>
+        <v>490442</v>
       </c>
       <c r="R19" t="n">
-        <v>6687970</v>
+        <v>6687947</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2727,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2880,10 +2885,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298069</v>
+        <v>130298026</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,16 +2896,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2911,7 +2916,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2920,10 +2925,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490458</v>
+        <v>490503</v>
       </c>
       <c r="R21" t="n">
-        <v>6687937</v>
+        <v>6687970</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2955,7 +2960,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2965,12 +2970,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -2525,38 +2525,47 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298069</v>
+        <v>130297996</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2565,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490458</v>
+        <v>490492</v>
       </c>
       <c r="R18" t="n">
-        <v>6687937</v>
+        <v>6687981</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,12 +2619,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Spridda över ca 1 kvm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2759,47 +2768,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130297996</v>
+        <v>130298026</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490492</v>
+        <v>490503</v>
       </c>
       <c r="R20" t="n">
-        <v>6687981</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2853,12 +2853,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spridda över ca 1 kvm.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,10 +2880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298026</v>
+        <v>130298069</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,16 +2891,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2916,7 +2911,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2925,10 +2920,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490503</v>
+        <v>490458</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687937</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2960,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2970,7 +2965,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R5" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R6" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -2179,45 +2179,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130297999</v>
+        <v>130298189</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490490</v>
+        <v>490428</v>
       </c>
       <c r="R15" t="n">
-        <v>6687978</v>
+        <v>6687892</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2249,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2264,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riktigt över större yta.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,50 +2296,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298189</v>
+        <v>130297999</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490428</v>
+        <v>490490</v>
       </c>
       <c r="R16" t="n">
-        <v>6687892</v>
+        <v>6687978</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Riktigt över större yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,47 +2525,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130297996</v>
+        <v>130298069</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2574,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490492</v>
+        <v>490458</v>
       </c>
       <c r="R18" t="n">
-        <v>6687981</v>
+        <v>6687937</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2609,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,12 +2610,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spridda över ca 1 kvm.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2880,38 +2871,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298069</v>
+        <v>130297996</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490458</v>
+        <v>490492</v>
       </c>
       <c r="R21" t="n">
-        <v>6687937</v>
+        <v>6687981</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Spridda över ca 1 kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R5" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R6" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R5" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R6" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297823</v>
+        <v>130297899</v>
       </c>
       <c r="B7" t="n">
         <v>57823</v>
@@ -1290,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490352</v>
+        <v>490357</v>
       </c>
       <c r="R7" t="n">
-        <v>6688068</v>
+        <v>6688094</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130297899</v>
+        <v>130297823</v>
       </c>
       <c r="B8" t="n">
         <v>57823</v>
@@ -1402,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490357</v>
+        <v>490352</v>
       </c>
       <c r="R8" t="n">
-        <v>6688094</v>
+        <v>6688068</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1843,45 +1843,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B12" t="n">
-        <v>81165</v>
+        <v>57667</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R12" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1928,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,50 +1960,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B13" t="n">
-        <v>57667</v>
+        <v>81165</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R13" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,12 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130148186</v>
       </c>
       <c r="B3" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297899</v>
+        <v>130297823</v>
       </c>
       <c r="B7" t="n">
         <v>57823</v>
@@ -1290,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490357</v>
+        <v>490352</v>
       </c>
       <c r="R7" t="n">
-        <v>6688094</v>
+        <v>6688068</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130297823</v>
+        <v>130297899</v>
       </c>
       <c r="B8" t="n">
         <v>57823</v>
@@ -1402,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490352</v>
+        <v>490357</v>
       </c>
       <c r="R8" t="n">
-        <v>6688068</v>
+        <v>6688094</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1843,50 +1843,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B12" t="n">
-        <v>57667</v>
+        <v>81168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R12" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,45 +1950,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B13" t="n">
-        <v>81165</v>
+        <v>57667</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R13" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2035,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,50 +2179,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298189</v>
+        <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490428</v>
+        <v>490490</v>
       </c>
       <c r="R15" t="n">
-        <v>6687892</v>
+        <v>6687978</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,12 +2259,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Riktigt över större yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,45 +2291,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130297999</v>
+        <v>130298189</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490490</v>
+        <v>490428</v>
       </c>
       <c r="R16" t="n">
-        <v>6687978</v>
+        <v>6687892</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt över större yta.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2874,7 +2874,7 @@
         <v>130297996</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130148294</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130148186</v>
       </c>
       <c r="B3" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>130150005</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R5" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R6" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1262,7 @@
         <v>130297823</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130297899</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130297886</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>130298148</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>130297865</v>
       </c>
       <c r="B12" t="n">
-        <v>81168</v>
+        <v>81194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>130297824</v>
       </c>
       <c r="B13" t="n">
-        <v>57667</v>
+        <v>57693</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130297822</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130298189</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>130298036</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>130298026</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>130298069</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>130298072</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>130297996</v>
       </c>
       <c r="B21" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>130297829</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>130297890</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -2525,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298026</v>
+        <v>130298069</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490503</v>
+        <v>490458</v>
       </c>
       <c r="R18" t="n">
-        <v>6687970</v>
+        <v>6687937</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2610,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,7 +2642,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298069</v>
+        <v>130298072</v>
       </c>
       <c r="B19" t="n">
         <v>57852</v>
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490458</v>
+        <v>490442</v>
       </c>
       <c r="R19" t="n">
-        <v>6687937</v>
+        <v>6687947</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2712,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2754,10 +2759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298072</v>
+        <v>130298026</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,16 +2770,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2785,7 +2790,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2794,10 +2799,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490442</v>
+        <v>490503</v>
       </c>
       <c r="R20" t="n">
-        <v>6687947</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2829,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,12 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130148186</v>
       </c>
       <c r="B3" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297823</v>
+        <v>130297899</v>
       </c>
       <c r="B7" t="n">
         <v>57849</v>
@@ -1290,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490352</v>
+        <v>490357</v>
       </c>
       <c r="R7" t="n">
-        <v>6688068</v>
+        <v>6688094</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130297899</v>
+        <v>130297823</v>
       </c>
       <c r="B8" t="n">
         <v>57849</v>
@@ -1402,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490357</v>
+        <v>490352</v>
       </c>
       <c r="R8" t="n">
-        <v>6688094</v>
+        <v>6688068</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298069</v>
+        <v>130298026</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490458</v>
+        <v>490503</v>
       </c>
       <c r="R18" t="n">
-        <v>6687937</v>
+        <v>6687970</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,12 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,7 +2637,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298072</v>
+        <v>130298069</v>
       </c>
       <c r="B19" t="n">
         <v>57852</v>
@@ -2682,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490442</v>
+        <v>490458</v>
       </c>
       <c r="R19" t="n">
-        <v>6687947</v>
+        <v>6687937</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2717,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2722,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2759,10 +2754,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298026</v>
+        <v>130298072</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,16 +2765,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2790,7 +2785,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2799,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490503</v>
+        <v>490442</v>
       </c>
       <c r="R20" t="n">
-        <v>6687970</v>
+        <v>6687947</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2834,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2844,7 +2839,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,7 +2874,7 @@
         <v>130297996</v>
       </c>
       <c r="B21" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>130148186</v>
       </c>
       <c r="B3" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R5" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R6" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297899</v>
+        <v>130297823</v>
       </c>
       <c r="B7" t="n">
         <v>57849</v>
@@ -1290,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490357</v>
+        <v>490352</v>
       </c>
       <c r="R7" t="n">
-        <v>6688094</v>
+        <v>6688068</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130297823</v>
+        <v>130297899</v>
       </c>
       <c r="B8" t="n">
         <v>57849</v>
@@ -1402,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490352</v>
+        <v>490357</v>
       </c>
       <c r="R8" t="n">
-        <v>6688068</v>
+        <v>6688094</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1843,45 +1843,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B12" t="n">
-        <v>81194</v>
+        <v>57693</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R12" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1928,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,50 +1960,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B13" t="n">
-        <v>57693</v>
+        <v>81194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R13" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,12 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2182,7 +2182,7 @@
         <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>130297996</v>
       </c>
       <c r="B21" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>130297821</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>130298224</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>130297823</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130297899</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130297886</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>130298148</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>130297824</v>
       </c>
       <c r="B12" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>130297865</v>
       </c>
       <c r="B13" t="n">
-        <v>81194</v>
+        <v>81196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130297822</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130298189</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>130298036</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,38 +2525,47 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298026</v>
+        <v>130297996</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>98953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2565,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490503</v>
+        <v>490492</v>
       </c>
       <c r="R18" t="n">
-        <v>6687970</v>
+        <v>6687981</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2619,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spridda över ca 1 kvm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298069</v>
+        <v>130298026</v>
       </c>
       <c r="B19" t="n">
-        <v>57852</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2648,16 +2662,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2668,7 +2682,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2677,10 +2691,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490458</v>
+        <v>490503</v>
       </c>
       <c r="R19" t="n">
-        <v>6687937</v>
+        <v>6687970</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2712,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,12 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298072</v>
+        <v>130298069</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490442</v>
+        <v>490458</v>
       </c>
       <c r="R20" t="n">
-        <v>6687947</v>
+        <v>6687937</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2829,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2871,47 +2880,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130297996</v>
+        <v>130298072</v>
       </c>
       <c r="B21" t="n">
-        <v>98951</v>
+        <v>57854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490492</v>
+        <v>490442</v>
       </c>
       <c r="R21" t="n">
-        <v>6687981</v>
+        <v>6687947</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spridda över ca 1 kvm.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,7 +3000,7 @@
         <v>130297829</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>130297890</v>
       </c>
       <c r="B23" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1843,50 +1843,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B12" t="n">
-        <v>57695</v>
+        <v>81196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R12" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,45 +1950,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B13" t="n">
-        <v>81196</v>
+        <v>57695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R13" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2035,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,45 +2179,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130297999</v>
+        <v>130298189</v>
       </c>
       <c r="B15" t="n">
-        <v>98953</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490490</v>
+        <v>490428</v>
       </c>
       <c r="R15" t="n">
-        <v>6687978</v>
+        <v>6687892</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2249,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2264,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riktigt över större yta.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,50 +2296,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298189</v>
+        <v>130297999</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490428</v>
+        <v>490490</v>
       </c>
       <c r="R16" t="n">
-        <v>6687892</v>
+        <v>6687978</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Riktigt över större yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,47 +2525,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130297996</v>
+        <v>130298026</v>
       </c>
       <c r="B18" t="n">
-        <v>98953</v>
+        <v>57851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2574,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490492</v>
+        <v>490503</v>
       </c>
       <c r="R18" t="n">
-        <v>6687981</v>
+        <v>6687970</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2609,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,12 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spridda över ca 1 kvm.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,10 +2637,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298026</v>
+        <v>130298069</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,16 +2648,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2682,7 +2668,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2691,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490503</v>
+        <v>490458</v>
       </c>
       <c r="R19" t="n">
-        <v>6687970</v>
+        <v>6687937</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2726,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2722,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,7 +2754,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298069</v>
+        <v>130298072</v>
       </c>
       <c r="B20" t="n">
         <v>57854</v>
@@ -2803,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490458</v>
+        <v>490442</v>
       </c>
       <c r="R20" t="n">
-        <v>6687937</v>
+        <v>6687947</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2838,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2880,38 +2871,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298072</v>
+        <v>130297996</v>
       </c>
       <c r="B21" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490442</v>
+        <v>490492</v>
       </c>
       <c r="R21" t="n">
-        <v>6687947</v>
+        <v>6687981</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Spridda över ca 1 kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R5" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R6" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1843,45 +1843,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B12" t="n">
-        <v>81196</v>
+        <v>57695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R12" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1928,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,50 +1960,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B13" t="n">
-        <v>57695</v>
+        <v>81196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R13" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,12 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,50 +2179,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298189</v>
+        <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490428</v>
+        <v>490490</v>
       </c>
       <c r="R15" t="n">
-        <v>6687892</v>
+        <v>6687978</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,12 +2259,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Riktigt över större yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,45 +2291,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130297999</v>
+        <v>130298189</v>
       </c>
       <c r="B16" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490490</v>
+        <v>490428</v>
       </c>
       <c r="R16" t="n">
-        <v>6687978</v>
+        <v>6687892</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt över större yta.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1843,50 +1843,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B12" t="n">
-        <v>57695</v>
+        <v>81196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R12" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,45 +1950,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B13" t="n">
-        <v>81196</v>
+        <v>57695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R13" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2035,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,45 +2179,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130297999</v>
+        <v>130298189</v>
       </c>
       <c r="B15" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490490</v>
+        <v>490428</v>
       </c>
       <c r="R15" t="n">
-        <v>6687978</v>
+        <v>6687892</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2249,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2264,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riktigt över större yta.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,50 +2296,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298189</v>
+        <v>130297999</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490428</v>
+        <v>490490</v>
       </c>
       <c r="R16" t="n">
-        <v>6687892</v>
+        <v>6687978</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Riktigt över större yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298026</v>
+        <v>130298069</v>
       </c>
       <c r="B18" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490503</v>
+        <v>490458</v>
       </c>
       <c r="R18" t="n">
-        <v>6687970</v>
+        <v>6687937</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2610,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298069</v>
+        <v>130298026</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2648,16 +2653,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2668,7 +2673,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490458</v>
+        <v>490503</v>
       </c>
       <c r="R19" t="n">
-        <v>6687937</v>
+        <v>6687970</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2712,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,12 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R5" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R6" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297823</v>
+        <v>130297899</v>
       </c>
       <c r="B7" t="n">
         <v>57851</v>
@@ -1290,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490352</v>
+        <v>490357</v>
       </c>
       <c r="R7" t="n">
-        <v>6688068</v>
+        <v>6688094</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130297899</v>
+        <v>130297823</v>
       </c>
       <c r="B8" t="n">
         <v>57851</v>
@@ -1402,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490357</v>
+        <v>490352</v>
       </c>
       <c r="R8" t="n">
-        <v>6688094</v>
+        <v>6688068</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1843,45 +1843,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B12" t="n">
-        <v>81196</v>
+        <v>57695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R12" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1928,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,50 +1960,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B13" t="n">
-        <v>57695</v>
+        <v>81196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R13" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,12 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298026</v>
+        <v>130298072</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,16 +2653,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2673,7 +2673,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490503</v>
+        <v>490442</v>
       </c>
       <c r="R19" t="n">
-        <v>6687970</v>
+        <v>6687947</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2727,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,10 +2759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298072</v>
+        <v>130298026</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,16 +2770,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2785,7 +2790,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2794,10 +2799,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490442</v>
+        <v>490503</v>
       </c>
       <c r="R20" t="n">
-        <v>6687947</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2829,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,12 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R5" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R6" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297899</v>
+        <v>130297823</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490357</v>
+        <v>490352</v>
       </c>
       <c r="R7" t="n">
-        <v>6688094</v>
+        <v>6688068</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130297823</v>
+        <v>130297899</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490352</v>
+        <v>490357</v>
       </c>
       <c r="R8" t="n">
-        <v>6688068</v>
+        <v>6688094</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,7 +1486,7 @@
         <v>130297886</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>130298148</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>130297824</v>
       </c>
       <c r="B12" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>130297865</v>
       </c>
       <c r="B13" t="n">
-        <v>81196</v>
+        <v>81204</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130297822</v>
       </c>
       <c r="B14" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>130298189</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>130297999</v>
       </c>
       <c r="B16" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>130298036</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>130298069</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>130298072</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,38 +2759,47 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298026</v>
+        <v>130297996</v>
       </c>
       <c r="B20" t="n">
-        <v>57851</v>
+        <v>98970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2799,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490503</v>
+        <v>490492</v>
       </c>
       <c r="R20" t="n">
-        <v>6687970</v>
+        <v>6687981</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2834,7 +2843,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2844,7 +2853,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spridda över ca 1 kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,47 +2885,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130297996</v>
+        <v>130298026</v>
       </c>
       <c r="B21" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2920,10 +2925,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490492</v>
+        <v>490503</v>
       </c>
       <c r="R21" t="n">
-        <v>6687981</v>
+        <v>6687970</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2955,7 +2960,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2965,12 +2970,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spridda över ca 1 kvm.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,7 +3000,7 @@
         <v>130297829</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>130297890</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130298224</v>
+        <v>130297821</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490361</v>
+        <v>490358</v>
       </c>
       <c r="R5" t="n">
-        <v>6688015</v>
+        <v>6688096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130297821</v>
+        <v>130298224</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1173,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490358</v>
+        <v>490361</v>
       </c>
       <c r="R6" t="n">
-        <v>6688096</v>
+        <v>6688015</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ganska färska hackspår.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1262,7 @@
         <v>130297823</v>
       </c>
       <c r="B7" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130297899</v>
       </c>
       <c r="B8" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130297886</v>
       </c>
       <c r="B9" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>130298148</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,50 +1843,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297824</v>
+        <v>130297865</v>
       </c>
       <c r="B12" t="n">
-        <v>57703</v>
+        <v>81205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490349</v>
+        <v>490429</v>
       </c>
       <c r="R12" t="n">
-        <v>6688055</v>
+        <v>6687934</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,45 +1950,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297865</v>
+        <v>130297824</v>
       </c>
       <c r="B13" t="n">
-        <v>81204</v>
+        <v>57704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490429</v>
+        <v>490349</v>
       </c>
       <c r="R13" t="n">
-        <v>6687934</v>
+        <v>6688055</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2035,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,7 +2070,7 @@
         <v>130297822</v>
       </c>
       <c r="B14" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,50 +2179,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130298189</v>
+        <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>57862</v>
+        <v>98971</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490428</v>
+        <v>490490</v>
       </c>
       <c r="R15" t="n">
-        <v>6687892</v>
+        <v>6687978</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,12 +2259,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Riktigt över större yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,45 +2291,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130297999</v>
+        <v>130298189</v>
       </c>
       <c r="B16" t="n">
-        <v>98970</v>
+        <v>57863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490490</v>
+        <v>490428</v>
       </c>
       <c r="R16" t="n">
-        <v>6687978</v>
+        <v>6687892</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt över större yta.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,7 +2411,7 @@
         <v>130298036</v>
       </c>
       <c r="B17" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>130298069</v>
       </c>
       <c r="B18" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>130298072</v>
       </c>
       <c r="B19" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>130297996</v>
       </c>
       <c r="B20" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>130298026</v>
       </c>
       <c r="B21" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>130297829</v>
       </c>
       <c r="B22" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>130297890</v>
       </c>
       <c r="B23" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>130297821</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>130298224</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>130297823</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130297899</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,50 +1483,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130297886</v>
+        <v>130297967</v>
       </c>
       <c r="B9" t="n">
-        <v>57863</v>
+        <v>98974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490364</v>
+        <v>490493</v>
       </c>
       <c r="R9" t="n">
-        <v>6688081</v>
+        <v>6687991</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,12 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Bladrosetter över ca 5 kvdm.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,59 +1609,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130297967</v>
+        <v>130297886</v>
       </c>
       <c r="B10" t="n">
-        <v>98971</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490493</v>
+        <v>490364</v>
       </c>
       <c r="R10" t="n">
-        <v>6687991</v>
+        <v>6688081</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bladrosetter över ca 5 kvdm.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,7 +1729,7 @@
         <v>130298148</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>130297865</v>
       </c>
       <c r="B12" t="n">
-        <v>81205</v>
+        <v>81206</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>130297824</v>
       </c>
       <c r="B13" t="n">
-        <v>57704</v>
+        <v>57705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130297822</v>
       </c>
       <c r="B14" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>130297999</v>
       </c>
       <c r="B15" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130298189</v>
       </c>
       <c r="B16" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>130298036</v>
       </c>
       <c r="B17" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>130298069</v>
       </c>
       <c r="B18" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>130298072</v>
       </c>
       <c r="B19" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,47 +2759,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130297996</v>
+        <v>130298026</v>
       </c>
       <c r="B20" t="n">
-        <v>98971</v>
+        <v>57861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2808,10 +2799,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490492</v>
+        <v>490503</v>
       </c>
       <c r="R20" t="n">
-        <v>6687981</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2843,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2853,12 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spridda över ca 1 kvm.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,38 +2871,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130298026</v>
+        <v>130297996</v>
       </c>
       <c r="B21" t="n">
-        <v>57860</v>
+        <v>98974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2925,10 +2920,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490503</v>
+        <v>490492</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687981</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2960,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2970,7 +2965,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spridda över ca 1 kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,7 +3000,7 @@
         <v>130297829</v>
       </c>
       <c r="B22" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>130297890</v>
       </c>
       <c r="B23" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -1483,59 +1483,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130297967</v>
+        <v>130297886</v>
       </c>
       <c r="B9" t="n">
-        <v>98974</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490493</v>
+        <v>490364</v>
       </c>
       <c r="R9" t="n">
-        <v>6687991</v>
+        <v>6688081</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1567,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1568,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Bladrosetter över ca 5 kvdm.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,50 +1600,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130297886</v>
+        <v>130297967</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>98974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490364</v>
+        <v>490493</v>
       </c>
       <c r="R10" t="n">
-        <v>6688081</v>
+        <v>6687991</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Bladrosetter över ca 5 kvdm.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298069</v>
+        <v>130298026</v>
       </c>
       <c r="B18" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490458</v>
+        <v>490503</v>
       </c>
       <c r="R18" t="n">
-        <v>6687937</v>
+        <v>6687970</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,12 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,7 +2637,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298072</v>
+        <v>130298069</v>
       </c>
       <c r="B19" t="n">
         <v>57864</v>
@@ -2682,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490442</v>
+        <v>490458</v>
       </c>
       <c r="R19" t="n">
-        <v>6687947</v>
+        <v>6687937</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2717,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2722,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2759,10 +2754,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298026</v>
+        <v>130298072</v>
       </c>
       <c r="B20" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,16 +2765,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2790,7 +2785,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2799,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490503</v>
+        <v>490442</v>
       </c>
       <c r="R20" t="n">
-        <v>6687970</v>
+        <v>6687947</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2834,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2844,7 +2839,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3224,6 +3224,128 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130909791</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57044</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oxmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490356</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6688166</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57701-2025 artfynd.xlsx
+++ b/artfynd/A 57701-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130148294</v>
+        <v>130297865</v>
       </c>
       <c r="B2" t="n">
-        <v>57033</v>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,56 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490399</v>
+        <v>490429</v>
       </c>
       <c r="R2" t="n">
-        <v>6688095</v>
+        <v>6687934</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två järpar Hanen svarar på min vissling</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -809,7 +785,7 @@
         <v>130148186</v>
       </c>
       <c r="B3" t="n">
-        <v>91723</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130150005</v>
+        <v>130297821</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,14 +925,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Oxmyran, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490442</v>
+        <v>490358</v>
       </c>
       <c r="R4" t="n">
-        <v>6687975</v>
+        <v>6688096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,22 +959,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ganska färska hackspår.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,26 +994,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130297821</v>
+        <v>130297822</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1065,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490358</v>
+        <v>490363</v>
       </c>
       <c r="R5" t="n">
-        <v>6688096</v>
+        <v>6688092</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ganska färska hackspår.</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,27 +1118,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130298224</v>
+        <v>130297823</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,19 +1149,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490361</v>
+        <v>490352</v>
       </c>
       <c r="R6" t="n">
-        <v>6688015</v>
+        <v>6688068</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,14 +1230,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130297823</v>
+        <v>130297829</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1295,14 +1266,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490352</v>
+        <v>490409</v>
       </c>
       <c r="R7" t="n">
-        <v>6688068</v>
+        <v>6687932</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,11 +1345,11 @@
         <v>130297899</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1483,27 +1454,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130297886</v>
+        <v>130298026</v>
       </c>
       <c r="B9" t="n">
-        <v>57864</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1514,19 +1485,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490364</v>
+        <v>490503</v>
       </c>
       <c r="R9" t="n">
-        <v>6688081</v>
+        <v>6687970</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,12 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:43</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,62 +1566,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130297967</v>
+        <v>106013896</v>
       </c>
       <c r="B10" t="n">
-        <v>98974</v>
+        <v>56766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100077</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Sulten bäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490493</v>
+        <v>490518</v>
       </c>
       <c r="R10" t="n">
-        <v>6687991</v>
+        <v>6687895</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,27 +1639,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:07</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:07</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bladrosetter över ca 5 kvdm.</t>
+          <t>Två uttrar som följs åt alldeles färska spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,22 +1664,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Fredrik Perols</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Fredrik Perols</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130298148</v>
+        <v>130150005</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,14 +1712,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490478</v>
+        <v>490442</v>
       </c>
       <c r="R11" t="n">
-        <v>6687986</v>
+        <v>6687975</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1796,34 +1746,29 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Barkfläk gran, hagelsalva.</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1831,22 +1776,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130297865</v>
+        <v>130297886</v>
       </c>
       <c r="B12" t="n">
-        <v>81206</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,34 +1799,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490429</v>
+        <v>490364</v>
       </c>
       <c r="R12" t="n">
-        <v>6687934</v>
+        <v>6688081</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1873,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,27 +1905,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130297824</v>
+        <v>130297890</v>
       </c>
       <c r="B13" t="n">
-        <v>57705</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1981,19 +1936,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490349</v>
+        <v>490365</v>
       </c>
       <c r="R13" t="n">
-        <v>6688055</v>
+        <v>6688077</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,12 +1990,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Höstläte.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130297822</v>
+        <v>130298036</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,16 +2033,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2098,19 +2053,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490363</v>
+        <v>490489</v>
       </c>
       <c r="R14" t="n">
-        <v>6688092</v>
+        <v>6687960</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2142,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2107,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,45 +2139,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130297999</v>
+        <v>130298069</v>
       </c>
       <c r="B15" t="n">
-        <v>98974</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490490</v>
+        <v>490458</v>
       </c>
       <c r="R15" t="n">
-        <v>6687978</v>
+        <v>6687937</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2249,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2224,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riktigt över större yta.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130298189</v>
+        <v>130298072</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490428</v>
+        <v>490442</v>
       </c>
       <c r="R16" t="n">
-        <v>6687892</v>
+        <v>6687947</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2366,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2408,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130298036</v>
+        <v>130298148</v>
       </c>
       <c r="B17" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2404,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2448,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490489</v>
+        <v>490478</v>
       </c>
       <c r="R17" t="n">
-        <v>6687960</v>
+        <v>6687986</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2483,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,19 +2458,19 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Barkfläk gran, hagelsalva.</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2525,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130298026</v>
+        <v>130298189</v>
       </c>
       <c r="B18" t="n">
-        <v>57861</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,16 +2501,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2556,7 +2521,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2565,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490503</v>
+        <v>490428</v>
       </c>
       <c r="R18" t="n">
-        <v>6687970</v>
+        <v>6687892</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2600,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2575,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130298069</v>
+        <v>130298224</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,10 +2647,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490458</v>
+        <v>490361</v>
       </c>
       <c r="R19" t="n">
-        <v>6687937</v>
+        <v>6688015</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2712,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2692,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2754,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130298072</v>
+        <v>130902224</v>
       </c>
       <c r="B20" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,19 +2755,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490442</v>
+        <v>490336</v>
       </c>
       <c r="R20" t="n">
-        <v>6687947</v>
+        <v>6688189</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2824,27 +2794,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flagplockad gran Massor av flagor på marken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,44 +2829,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130297996</v>
+        <v>130148294</v>
       </c>
       <c r="B21" t="n">
-        <v>98974</v>
+        <v>57132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2904,29 +2874,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490492</v>
+        <v>490399</v>
       </c>
       <c r="R21" t="n">
-        <v>6687981</v>
+        <v>6688095</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,27 +2925,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Spridda över ca 1 kvm.</t>
+          <t>Två järpar Hanen svarar på min vissling</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,39 +2960,39 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130297829</v>
+        <v>130909791</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>57132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3026,21 +3001,31 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+          <t>Oxmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490409</v>
+        <v>490356</v>
       </c>
       <c r="R22" t="n">
-        <v>6687932</v>
+        <v>6688166</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3067,22 +3052,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,22 +3082,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130297890</v>
+        <v>130297824</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>57794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,16 +3105,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3140,19 +3125,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490365</v>
+        <v>490349</v>
       </c>
       <c r="R23" t="n">
-        <v>6688077</v>
+        <v>6688055</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3184,7 +3169,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,12 +3179,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,60 +3211,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130909791</v>
+        <v>130297967</v>
       </c>
       <c r="B24" t="n">
-        <v>57064</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oxmyran, Dlr</t>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490356</v>
+        <v>490493</v>
       </c>
       <c r="R24" t="n">
-        <v>6688166</v>
+        <v>6687991</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3306,22 +3290,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bladrosetter över ca 5 kvdm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,15 +3325,253 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130297996</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490492</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6687981</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridda över ca 1 kvm.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130297999</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hommanbergsknippan, Hommanbergsknippan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490490</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6687978</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riktigt över större yta.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
